--- a/test-output/CarWashServices.xlsx
+++ b/test-output/CarWashServices.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="22">
   <si>
     <t>#</t>
   </si>
@@ -27,6 +27,57 @@
   </si>
   <si>
     <t>Location</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>Car Washing Service</t>
+  </si>
+  <si>
+    <t>DM Car Care</t>
+  </si>
+  <si>
+    <t>4.7</t>
+  </si>
+  <si>
+    <t>Chennai</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>Car Washing Services At Home</t>
+  </si>
+  <si>
+    <t>Infinity Solutions</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>Sree Shan Motors</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>Car And Bike Foam Wash</t>
+  </si>
+  <si>
+    <t>DP Car Spa</t>
+  </si>
+  <si>
+    <t>Car Foam Washing Services</t>
+  </si>
+  <si>
+    <t>Sparkle Car Care</t>
+  </si>
+  <si>
+    <t>N/A</t>
   </si>
 </sst>
 </file>
@@ -90,12 +141,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:E1"/>
+  <dimension ref="A1:E6"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="1.9296875" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="12.12890625" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="14.0" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="25.46484375" customWidth="true" bestFit="true"/>
+    <col min="3" max="3" width="15.1953125" customWidth="true" bestFit="true"/>
     <col min="4" max="4" width="6.1953125" customWidth="true" bestFit="true"/>
     <col min="5" max="5" width="7.9296875" customWidth="true" bestFit="true"/>
   </cols>
@@ -117,6 +168,91 @@
         <v>4</v>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="s" s="0">
+        <v>5</v>
+      </c>
+      <c r="B2" t="s" s="0">
+        <v>6</v>
+      </c>
+      <c r="C2" t="s" s="0">
+        <v>7</v>
+      </c>
+      <c r="D2" t="s" s="0">
+        <v>8</v>
+      </c>
+      <c r="E2" t="s" s="0">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="B3" t="s" s="0">
+        <v>11</v>
+      </c>
+      <c r="C3" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="D3" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="E3" t="s" s="0">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="B4" t="s" s="0">
+        <v>6</v>
+      </c>
+      <c r="C4" t="s" s="0">
+        <v>15</v>
+      </c>
+      <c r="D4" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="E4" t="s" s="0">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s" s="0">
+        <v>16</v>
+      </c>
+      <c r="B5" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="C5" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="D5" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="E5" t="s" s="0">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="B6" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="C6" t="s" s="0">
+        <v>20</v>
+      </c>
+      <c r="D6" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="E6" t="s" s="0">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
